--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64963_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64963_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R16f22d9c701f4461"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rfa108648b9ff4ce2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    535.0161</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    512.9567</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    598.5348</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    632.6409</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    577.2576</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    517.6433</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    468.9942</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    424.2495</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    431.1333</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64963_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_64963_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rfa108648b9ff4ce2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R1b51eb663b79444a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    678.6372</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    575.8427</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    439.8945</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    469.8476</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    455.0702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    505.3178</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    536.4242</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    619.8120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    760.9299</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    969.3213</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    703.9821</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    600.9836</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    702.0367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    609.3299</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    463.5185</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    483.7005</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    617.0639</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    525.3162</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    483.0747</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    527.6630</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    648.1295</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    699.0165</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    740.1221</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    727.1367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    674.8824</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    665.4954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    482.4489</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    376.8452</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    413.6109</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    471.6539</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    493.2440</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    522.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    471.3410</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    413.9238</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    414.0803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    420.3383</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    426.2834</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    420.6512</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    413.7674</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    397.1837</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    414.3932</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    423.9366</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    479.8505</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    533.4516</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    632.9538</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    756.2364</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    648.9117</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    548.6273</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
